--- a/Gantt-chart TIMELINE related BC per 17 Maret 2026.xlsx
+++ b/Gantt-chart TIMELINE related BC per 17 Maret 2026.xlsx
@@ -1738,21 +1738,6 @@
     <t>BC app development</t>
   </si>
   <si>
-    <t>Menu Beacukai, Sub Menu Update Dok Keluar Market, Form Traceability Belum Ada Di MCS LJK</t>
-  </si>
-  <si>
-    <t>Menu Beacukai, Sub Menu Update Dok Non-Keluar Market, Form Traceability Belum Ada Di MCS LJK</t>
-  </si>
-  <si>
-    <t>Menu Laporan Keluar/Masuk, Sub Menu Balance Lokal Belum Ada Di MCS LJK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menu Print, Sub menu Packing List Dan Invoice Belum Ada Di MCS LJK </t>
-  </si>
-  <si>
-    <t>Menu Mutasi, Sub menu Bahan Bakar Belum Ada Di IT INVENTORY LJK</t>
-  </si>
-  <si>
     <t>11/UAK/03/2026</t>
   </si>
   <si>
@@ -1762,25 +1747,40 @@
     <t>02/UAK/11/2025</t>
   </si>
   <si>
-    <t>1a Menambah kolom : Asal Doc , No Daftar dan Tanggal daftar</t>
-  </si>
-  <si>
-    <t>1b Menambah menu Edit untuk Pengisian Asal DOC, No Daftar dan Tanggal Daftar</t>
-  </si>
-  <si>
-    <t>2 Belum tersedia untuk user LJK</t>
-  </si>
-  <si>
-    <t>3a penambahan kolom dengan nama QTY Keluar Tunggu Doc BC</t>
-  </si>
-  <si>
-    <t>3b saldo buku belum berkurang jika doc bc belum terupdate</t>
-  </si>
-  <si>
-    <t>4 Laporan mutasi yg muncul sesuai dengan user yang digunakan</t>
-  </si>
-  <si>
     <t>BC(75% BC, 25% SAP)</t>
+  </si>
+  <si>
+    <t>1a Menambah kolom : Asal Doc , No Daftar dan Tanggal daftar(/pzzl/index.php/Warehouse/laporanKeluar)</t>
+  </si>
+  <si>
+    <t>1b Menambah menu Edit untuk Pengisian Asal DOC, No Daftar dan Tanggal Daftar(/pzzl/index.php/Warehouse/laporanMasuk)</t>
+  </si>
+  <si>
+    <t>2 Belum tersedia untuk user LJK(/pzzl/index.php/MIT/dashboard)</t>
+  </si>
+  <si>
+    <t>3a penambahan kolom dengan nama QTY Keluar Tunggu Doc BC(/pzzl/index.php/Reporting/reportMR)</t>
+  </si>
+  <si>
+    <t>3b saldo buku belum berkurang jika doc bc belum terupdate(/pzzl/index.php/Reporting/reportMR)</t>
+  </si>
+  <si>
+    <t>4 Laporan mutasi yg muncul sesuai dengan user yang digunakan(/pzzl/index.php/Reporting/reportMR)</t>
+  </si>
+  <si>
+    <t>Menu Beacukai, Sub Menu Update Dok Keluar Market, Form Traceability Belum Ada Di MCS LJK [http://192.168.255.84/pzzl/index.php/Legal/updateKeluar2]</t>
+  </si>
+  <si>
+    <t>Menu Beacukai, Sub Menu Update Dok Non-Keluar Market, Form Traceability Belum Ada Di MCS LJK[http://192.168.255.84/pzzl/index.php/Legal/updateKeluar]</t>
+  </si>
+  <si>
+    <t>Menu Laporan Keluar/Masuk, Sub Menu Balance Lokal Belum Ada Di MCS LJK[http://192.168.255.84/pzzl/index.php/Legal/balancing\_local]</t>
+  </si>
+  <si>
+    <t>Menu Print, Sub menu Packing List Dan Invoice Belum Ada Di MCS LJK [http://192.168.255.84/pzzl/index.php/Legal/packingListInvoice]</t>
+  </si>
+  <si>
+    <t>Menu Mutasi, Sub menu Bahan Bakar Belum Ada Di IT INVENTORY LJK[http://192.168.255.84/leuwitex/beacukai/rMutBBM]</t>
   </si>
 </sst>
 </file>
@@ -3306,7 +3306,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>684068</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>227638</xdr:rowOff>
+      <xdr:rowOff>71774</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -4006,7 +4006,7 @@
   <sheetData>
     <row r="1" spans="1:66" ht="30" customHeight="1">
       <c r="A1" s="56" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4508,7 +4508,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E7" s="74" t="s">
         <v>7</v>
@@ -4830,19 +4830,19 @@
       <c r="BM8" s="88"/>
       <c r="BN8" s="88"/>
     </row>
-    <row r="9" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="9" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A9" s="4" t="str">
         <f t="shared" ref="A9:A19" si="5">IF(ISERROR(VALUE(SUBSTITUTE(prevWBS,".",""))),"0.1",IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",1))),prevWBS&amp;".1",LEFT(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1)))&amp;IF(ISERROR(FIND("`",SUBSTITUTE(prevWBS,".","`",2))),VALUE(RIGHT(prevWBS,LEN(prevWBS)-FIND("`",SUBSTITUTE(prevWBS,".","`",1))))+1,VALUE(MID(prevWBS,FIND("`",SUBSTITUTE(prevWBS,".","`",1))+1,(FIND("`",SUBSTITUTE(prevWBS,".","`",2))-FIND("`",SUBSTITUTE(prevWBS,".","`",1))-1)))+1)))</f>
         <v>1.1</v>
       </c>
       <c r="B9" s="107" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C9" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="119" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E9" s="102">
         <v>46107</v>
@@ -4919,19 +4919,19 @@
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
     </row>
-    <row r="10" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="10" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A10" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.2</v>
       </c>
       <c r="B10" s="107" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="C10" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="119" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E10" s="102">
         <v>46107</v>
@@ -5008,19 +5008,19 @@
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
     </row>
-    <row r="11" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="11" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A11" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.3</v>
       </c>
       <c r="B11" s="107" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C11" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E11" s="102">
         <v>46108</v>
@@ -5097,19 +5097,19 @@
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
     </row>
-    <row r="12" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="12" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A12" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.4</v>
       </c>
       <c r="B12" s="107" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C12" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E12" s="102">
         <v>46109</v>
@@ -5186,19 +5186,19 @@
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
     </row>
-    <row r="13" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="13" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A13" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.5</v>
       </c>
       <c r="B13" s="107" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C13" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D13" s="119" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E13" s="102">
         <v>46111</v>
@@ -5275,19 +5275,19 @@
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
     </row>
-    <row r="14" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="14" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A14" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.6</v>
       </c>
       <c r="B14" s="107" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C14" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D14" s="119" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E14" s="102">
         <v>46112</v>
@@ -5364,19 +5364,19 @@
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
     </row>
-    <row r="15" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="15" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A15" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.7</v>
       </c>
       <c r="B15" s="107" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C15" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="119" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E15" s="102">
         <v>46113</v>
@@ -5453,19 +5453,19 @@
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
     </row>
-    <row r="16" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="16" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A16" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
       <c r="B16" s="107" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C16" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="119" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E16" s="102">
         <v>46114</v>
@@ -5542,19 +5542,19 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
     </row>
-    <row r="17" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="17" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A17" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.9</v>
       </c>
       <c r="B17" s="107" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C17" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="119" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E17" s="102">
         <v>46115</v>
@@ -5631,19 +5631,19 @@
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
     </row>
-    <row r="18" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="18" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A18" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.10</v>
       </c>
       <c r="B18" s="107" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C18" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="119" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E18" s="102">
         <v>46116</v>
@@ -5720,19 +5720,19 @@
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
     </row>
-    <row r="19" spans="1:66" s="1" customFormat="1" ht="24" customHeight="1">
+    <row r="19" spans="1:66" s="1" customFormat="1" ht="36" customHeight="1">
       <c r="A19" s="4" t="str">
         <f t="shared" si="5"/>
         <v>1.11</v>
       </c>
       <c r="B19" s="107" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C19" s="90" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="119" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E19" s="102">
         <v>46117</v>
